--- a/設計書/テスト仕様書_異常系.xlsx
+++ b/設計書/テスト仕様書_異常系.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>既に別グループに参加済みの端末</t>
+          <t>同じグループへの重複参加</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>既に他グループのメンバーであるdevice_idで参加しようとする</t>
+          <t>既にそのグループのメンバーであるdevice_idで、同じグループへ再度参加しようとする</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>409相当のエラー(ALREADY_JOINED)を返し、二重参加させない</t>
+          <t>409相当のエラー(ALREADY_JOINED)を返し、二重登録させない(別グループへの参加は許可されるため対象外)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -956,6 +956,60 @@
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /members/:memberId (F19)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>管理者以外による他メンバー削除</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>管理者でないメンバーが、自分以外のmember_idに対して削除をリクエストする</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>403相当のエラーを返し、削除を拒否する</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /groups/:groupId (F20)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>管理者以外によるグループ削除</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>管理者でないメンバーがグループ削除をリクエストする</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>403相当のエラーを返し、削除を拒否する</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
